--- a/survey_templates/047_falling_kisses_feedback_form--survey_templates.xlsx
+++ b/survey_templates/047_falling_kisses_feedback_form--survey_templates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,13 +515,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>overall_rating</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What did you think about our service?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Rate from 1-5</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -538,13 +542,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rating_satisfaction</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How satisfied were you with our service?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rate from 1-5</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -561,13 +569,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rating_quality</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How would you rate the quality of our service?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rate from 1-5</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -584,13 +596,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rating_value</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Do you think you got value for money?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rate from 1-5</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -607,13 +623,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rating_presentation</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>How was the presentation of our service?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rate from 1-5</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -630,13 +650,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rating_service</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How would you rate the service experience?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rate from 1-5</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -653,13 +677,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rating_food_and_drinks</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>How was the food and drinks quality?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rate from 1-5</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -671,15 +699,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rating_value</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rating_value</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Any comments about our service?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please share your thoughts</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -694,15 +726,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rating_presentation</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rating_presentation</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Do you have any suggestions for us?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Help us improve</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -717,18 +753,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rating_service</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rating_service</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Email address</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please enter your email address</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -740,18 +780,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rating_food_and_drinks</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rating_food_and_drinks</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please enter your phone number</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -763,85 +807,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Additional comments or questions?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>If you have anything else you'd like to share, please do</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>suggestions</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>suggestions</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
